--- a/src/assets/soil-import-template.xlsx
+++ b/src/assets/soil-import-template.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="자제, 대표필지" sheetId="2" r:id="rId1"/>
     <sheet name="시료접수대장" sheetId="3" r:id="rId2"/>
-    <sheet name="일괄등록양식" sheetId="4" r:id="rId3"/>
+    <sheet name="공익직불제" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'자제, 대표필지'!$A$1:$O$5</definedName>
@@ -380,7 +380,7 @@
     <t>채취자명</t>
   </si>
   <si>
-    <t>분석의뢰일(접수일자)</t>
+    <t>시료채취일</t>
   </si>
   <si>
     <t>차수</t>

--- a/src/assets/soil-import-template.xlsx
+++ b/src/assets/soil-import-template.xlsx
@@ -1181,7 +1181,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>지구분</t>
+      <t>경지구분</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/src/assets/soil-import-template.xlsx
+++ b/src/assets/soil-import-template.xlsx
@@ -1157,21 +1157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
     <r>
       <rPr>
         <b/>
@@ -2744,9 +2729,7 @@
       <c r="F4" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="49" t="s">
-        <v>57</v>
-      </c>
+      <c r="G4" s="49"/>
       <c r="H4" s="49" t="s">
         <v>42</v>
       </c>
@@ -2864,7 +2847,7 @@
       <c r="Z5" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
@@ -2879,6 +2862,7 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/soil-import-template.xlsx
+++ b/src/assets/soil-import-template.xlsx
@@ -14,7 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="자제, 대표필지" sheetId="2" r:id="rId1"/>
-    <sheet name="시료접수대장" sheetId="3" r:id="rId2"/>
+    <sheet name="농가의뢰" sheetId="3" r:id="rId2"/>
     <sheet name="공익직불제" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -117,7 +117,7 @@
     <t>면적(m²)</t>
   </si>
   <si>
-    <t>작물</t>
+    <t>작물명 또는 작물코드</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
